--- a/output/Data and Chart Outputs/bhutan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/bhutan_power_generation_daily.xlsx
@@ -973,7 +973,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Flags: values blanked because they fall below 30% of the centred 15-day median of their series - BPSO's daily sheets carry occasional keying slips (e.g. 8,200 for 82,000 MWh).</t>
+          <t>Flags: values blanked because they fall below 30% (generation, energy met, peak: or above 4x) the centred 15-day median of their series - BPSO's daily sheets carry occasional keying slips (e.g. 8,200 for 82,000 MWh). BPSO's placeholder 99999.999 and negative energy values are blanked too (not listed).</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
         <v>46204</v>
       </c>
       <c r="B38" t="n">
-        <v>2405.468569</v>
+        <v>2305.46857</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -4734,9 +4734,6 @@
       <c r="D100" t="n">
         <v>17830</v>
       </c>
-      <c r="E100" t="n">
-        <v>99999.999</v>
-      </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
@@ -5290,6 +5287,9 @@
       <c r="D123" t="n">
         <v>17480</v>
       </c>
+      <c r="E123" t="n">
+        <v>387.4</v>
+      </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
@@ -5414,9 +5414,6 @@
       <c r="D128" t="n">
         <v>19816</v>
       </c>
-      <c r="E128" t="n">
-        <v>99999.999</v>
-      </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
@@ -5469,9 +5466,6 @@
       <c r="E130" t="n">
         <v>0</v>
       </c>
-      <c r="F130" t="n">
-        <v>-1131.865</v>
-      </c>
       <c r="G130" t="n">
         <v>860</v>
       </c>
@@ -5547,9 +5541,6 @@
       <c r="E133" t="n">
         <v>0</v>
       </c>
-      <c r="F133" t="n">
-        <v>-2540</v>
-      </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
@@ -5573,9 +5564,6 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
-      <c r="F134" t="n">
-        <v>-2710</v>
-      </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
@@ -5651,9 +5639,6 @@
       <c r="E137" t="n">
         <v>0</v>
       </c>
-      <c r="F137" t="n">
-        <v>-2565.588</v>
-      </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
@@ -5781,9 +5766,6 @@
       <c r="E142" t="n">
         <v>0</v>
       </c>
-      <c r="F142" t="n">
-        <v>-3226.183</v>
-      </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
@@ -5859,9 +5841,6 @@
       <c r="E145" t="n">
         <v>0</v>
       </c>
-      <c r="F145" t="n">
-        <v>-3830.61</v>
-      </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
@@ -5885,9 +5864,6 @@
       <c r="E146" t="n">
         <v>0</v>
       </c>
-      <c r="F146" t="n">
-        <v>-4843.455</v>
-      </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
@@ -8797,9 +8773,6 @@
       <c r="G258" t="n">
         <v>0</v>
       </c>
-      <c r="H258" t="n">
-        <v>-2182.332</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
@@ -24518,9 +24491,6 @@
       <c r="C866" t="n">
         <v>87962</v>
       </c>
-      <c r="D866" t="n">
-        <v>99999.999</v>
-      </c>
       <c r="E866" t="n">
         <v>49659</v>
       </c>
@@ -24615,12 +24585,6 @@
     <row r="870">
       <c r="A870" s="4" t="n">
         <v>46210</v>
-      </c>
-      <c r="B870" t="n">
-        <v>99999.999</v>
-      </c>
-      <c r="C870" t="n">
-        <v>99999.999</v>
       </c>
       <c r="D870" t="n">
         <v>35065.76</v>
@@ -34224,7 +34188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34614,7 +34578,7 @@
         <v>21.17</v>
       </c>
       <c r="D24" t="n">
-        <v>18413.6</v>
+        <v>17645.3</v>
       </c>
     </row>
     <row r="25">
@@ -34630,7 +34594,7 @@
         <v>14.195</v>
       </c>
       <c r="D25" t="n">
-        <v>11360</v>
+        <v>10243.9</v>
       </c>
     </row>
     <row r="26">
@@ -34715,7 +34679,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>45237</v>
+        <v>45239</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -34723,15 +34687,15 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>387.4</v>
+        <v>234</v>
       </c>
       <c r="D31" t="n">
-        <v>1800</v>
+        <v>1183.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>45239</v>
+        <v>45444</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -34739,15 +34703,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1800</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>45444</v>
+        <v>45445</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -34763,7 +34727,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>45445</v>
+        <v>45454</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -34771,15 +34735,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1644</v>
       </c>
       <c r="D34" t="n">
-        <v>2360</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>45454</v>
+        <v>45623</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -34787,15 +34751,15 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1644</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>6088</v>
+        <v>508</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>45623</v>
+        <v>46012</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -34806,12 +34770,12 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>508</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46012</v>
+        <v>46019</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -34822,12 +34786,12 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>74</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46019</v>
+        <v>46023</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -34838,12 +34802,12 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -34854,12 +34818,12 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46024</v>
+        <v>46033</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -34870,12 +34834,12 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46033</v>
+        <v>46044</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -34886,12 +34850,12 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -34902,12 +34866,12 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -34918,12 +34882,12 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -34939,7 +34903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -34947,7 +34911,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="D45" t="n">
         <v>187</v>
@@ -34955,7 +34919,7 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46048</v>
+        <v>46078</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -34963,15 +34927,15 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>187</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -34982,12 +34946,12 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -34998,12 +34962,12 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>75</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -35014,12 +34978,12 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>203</v>
+        <v>310.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46082</v>
+        <v>46149</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -35027,15 +34991,15 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="D50" t="n">
-        <v>310.1</v>
+        <v>798</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -35043,15 +35007,15 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>798</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -35062,12 +35026,12 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1130</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -35075,15 +35039,15 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="D53" t="n">
-        <v>1193</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46152</v>
+        <v>46154</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -35091,15 +35055,15 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>1754</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -35107,15 +35071,15 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>4196</v>
       </c>
       <c r="D55" t="n">
-        <v>3970</v>
+        <v>14298</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -35123,15 +35087,15 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4196</v>
+        <v>6.477</v>
       </c>
       <c r="D56" t="n">
-        <v>14298</v>
+        <v>13809</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>46175</v>
+        <v>46258</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -35139,25 +35103,9 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6.477</v>
+        <v>53.046</v>
       </c>
       <c r="D57" t="n">
-        <v>13809</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Exports_MWh</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>53.046</v>
-      </c>
-      <c r="D58" t="n">
         <v>49326</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/bhutan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/bhutan_power_generation_daily.xlsx
@@ -24,8 +24,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,12 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,6 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bhutan power generation (BPSO, hydro) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -462,6 +464,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bhutan peak demand (BPSO) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -977,7 +980,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -992,7 +994,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1067,7 +1068,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B2" t="n">
@@ -1093,7 +1094,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B3" t="n">
@@ -1119,7 +1120,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B4" t="n">
@@ -1145,7 +1146,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B5" t="n">
@@ -1171,7 +1172,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B6" t="n">
@@ -1197,7 +1198,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B7" t="n">
@@ -1223,7 +1224,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B8" t="n">
@@ -1249,7 +1250,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B9" t="n">
@@ -1275,7 +1276,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B10" t="n">
@@ -1301,7 +1302,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B11" t="n">
@@ -1327,7 +1328,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B12" t="n">
@@ -1353,7 +1354,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B13" t="n">
@@ -1379,7 +1380,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B14" t="n">
@@ -1405,7 +1406,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B15" t="n">
@@ -1431,7 +1432,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B16" t="n">
@@ -1457,7 +1458,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -1483,7 +1484,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B18" t="n">
@@ -1509,7 +1510,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B19" t="n">
@@ -1535,7 +1536,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B20" t="n">
@@ -1561,7 +1562,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B21" t="n">
@@ -1587,7 +1588,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B22" t="n">
@@ -1613,7 +1614,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="n">
@@ -1639,7 +1640,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B24" t="n">
@@ -1665,7 +1666,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B25" t="n">
@@ -1691,7 +1692,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B26" t="n">
@@ -1717,7 +1718,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B27" t="n">
@@ -1743,7 +1744,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B28" t="n">
@@ -1769,7 +1770,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B29" t="n">
@@ -1795,7 +1796,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B30" t="n">
@@ -1821,7 +1822,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B31" t="n">
@@ -1877,7 +1878,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B2" t="n">
@@ -1885,7 +1886,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B3" t="n">
@@ -1893,7 +1894,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B4" t="n">
@@ -1901,7 +1902,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B5" t="n">
@@ -1909,7 +1910,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B6" t="n">
@@ -1917,7 +1918,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B7" t="n">
@@ -1925,7 +1926,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B8" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B9" t="n">
@@ -1941,7 +1942,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B10" t="n">
@@ -1949,7 +1950,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B11" t="n">
@@ -1957,7 +1958,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B12" t="n">
@@ -1965,7 +1966,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B13" t="n">
@@ -1973,7 +1974,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B14" t="n">
@@ -1981,7 +1982,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B15" t="n">
@@ -1989,7 +1990,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B16" t="n">
@@ -1997,7 +1998,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -2005,7 +2006,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B18" t="n">
@@ -2013,7 +2014,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B19" t="n">
@@ -2021,7 +2022,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B20" t="n">
@@ -2029,7 +2030,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B21" t="n">
@@ -2037,7 +2038,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B22" t="n">
@@ -2045,7 +2046,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="n">
@@ -2053,7 +2054,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B24" t="n">
@@ -2061,7 +2062,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B25" t="n">
@@ -2069,7 +2070,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B26" t="n">
@@ -2077,7 +2078,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B27" t="n">
@@ -2085,7 +2086,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B28" t="n">
@@ -2093,7 +2094,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B29" t="n">
@@ -2101,7 +2102,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B30" t="n">
@@ -2109,7 +2110,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B31" t="n">
@@ -2117,7 +2118,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B32" t="n">
@@ -2125,7 +2126,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B33" t="n">
@@ -2133,7 +2134,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B34" t="n">
@@ -2141,7 +2142,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B35" t="n">
@@ -2149,7 +2150,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B36" t="n">

--- a/output/Data and Chart Outputs/bhutan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/bhutan_power_generation_daily.xlsx
@@ -24,8 +24,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,13 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -980,6 +979,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -990,10 +990,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2023-07-01 to 2026-10-03.</t>
+          <t>Daily from 2023-07-01 to 2026-10-26.</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1068,7 +1069,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B2" t="n">
@@ -1094,7 +1095,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B3" t="n">
@@ -1120,7 +1121,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B4" t="n">
@@ -1146,7 +1147,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B5" t="n">
@@ -1172,7 +1173,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B6" t="n">
@@ -1198,7 +1199,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B7" t="n">
@@ -1224,7 +1225,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B8" t="n">
@@ -1250,7 +1251,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B9" t="n">
@@ -1276,7 +1277,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B10" t="n">
@@ -1302,7 +1303,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B11" t="n">
@@ -1328,7 +1329,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B12" t="n">
@@ -1354,7 +1355,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B13" t="n">
@@ -1380,7 +1381,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B14" t="n">
@@ -1406,7 +1407,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B15" t="n">
@@ -1432,7 +1433,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B16" t="n">
@@ -1458,7 +1459,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -1484,7 +1485,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B18" t="n">
@@ -1510,7 +1511,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B19" t="n">
@@ -1536,7 +1537,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B20" t="n">
@@ -1562,7 +1563,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B21" t="n">
@@ -1588,7 +1589,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B22" t="n">
@@ -1614,7 +1615,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="n">
@@ -1640,7 +1641,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B24" t="n">
@@ -1666,7 +1667,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B25" t="n">
@@ -1692,7 +1693,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B26" t="n">
@@ -1718,7 +1719,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B27" t="n">
@@ -1744,7 +1745,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B28" t="n">
@@ -1770,7 +1771,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B29" t="n">
@@ -1796,7 +1797,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B30" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B31" t="n">
@@ -1878,7 +1879,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B2" t="n">
@@ -1886,7 +1887,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B3" t="n">
@@ -1894,7 +1895,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B4" t="n">
@@ -1902,7 +1903,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B5" t="n">
@@ -1910,7 +1911,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B6" t="n">
@@ -1918,7 +1919,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B7" t="n">
@@ -1926,7 +1927,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B8" t="n">
@@ -1934,7 +1935,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B9" t="n">
@@ -1942,7 +1943,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B10" t="n">
@@ -1950,7 +1951,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B11" t="n">
@@ -1958,7 +1959,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B12" t="n">
@@ -1966,7 +1967,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B13" t="n">
@@ -1974,7 +1975,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B14" t="n">
@@ -1982,7 +1983,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B15" t="n">
@@ -1990,7 +1991,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B16" t="n">
@@ -1998,7 +1999,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B17" t="n">
@@ -2006,7 +2007,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B18" t="n">
@@ -2014,7 +2015,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B19" t="n">
@@ -2022,7 +2023,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B20" t="n">
@@ -2030,7 +2031,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B21" t="n">
@@ -2038,7 +2039,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B22" t="n">
@@ -2046,7 +2047,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B23" t="n">
@@ -2054,7 +2055,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B24" t="n">
@@ -2062,7 +2063,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B25" t="n">
@@ -2070,7 +2071,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B26" t="n">
@@ -2078,7 +2079,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B27" t="n">
@@ -2086,7 +2087,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B28" t="n">
@@ -2094,7 +2095,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B29" t="n">
@@ -2102,7 +2103,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B30" t="n">
@@ -2110,7 +2111,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B31" t="n">
@@ -2118,7 +2119,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B32" t="n">
@@ -2126,7 +2127,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B33" t="n">
@@ -2134,7 +2135,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B34" t="n">
@@ -2142,7 +2143,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B35" t="n">
@@ -2150,11 +2151,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B36" t="n">
-        <v>1588.136666666667</v>
+        <v>1585.12</v>
       </c>
     </row>
   </sheetData>
@@ -2169,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K948"/>
+  <dimension ref="A1:K969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34840,6 +34841,738 @@
         <v>-38748</v>
       </c>
       <c r="K948" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B949" t="n">
+        <v>76416</v>
+      </c>
+      <c r="C949" t="n">
+        <v>76416</v>
+      </c>
+      <c r="D949" t="n">
+        <v>37240.951</v>
+      </c>
+      <c r="E949" t="n">
+        <v>39176</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0</v>
+      </c>
+      <c r="G949" t="n">
+        <v>0</v>
+      </c>
+      <c r="H949" t="n">
+        <v>0</v>
+      </c>
+      <c r="I949" t="n">
+        <v>2682.375</v>
+      </c>
+      <c r="J949" t="n">
+        <v>-39176</v>
+      </c>
+      <c r="K949" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B950" t="n">
+        <v>75772</v>
+      </c>
+      <c r="C950" t="n">
+        <v>75772</v>
+      </c>
+      <c r="D950" t="n">
+        <v>36687.69</v>
+      </c>
+      <c r="E950" t="n">
+        <v>39085</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0</v>
+      </c>
+      <c r="G950" t="n">
+        <v>0</v>
+      </c>
+      <c r="H950" t="n">
+        <v>0</v>
+      </c>
+      <c r="I950" t="n">
+        <v>32836.5</v>
+      </c>
+      <c r="J950" t="n">
+        <v>-39085</v>
+      </c>
+      <c r="K950" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B951" t="n">
+        <v>67720</v>
+      </c>
+      <c r="C951" t="n">
+        <v>67720</v>
+      </c>
+      <c r="D951" t="n">
+        <v>37120.13</v>
+      </c>
+      <c r="E951" t="n">
+        <v>30600</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0</v>
+      </c>
+      <c r="G951" t="n">
+        <v>0</v>
+      </c>
+      <c r="H951" t="n">
+        <v>0</v>
+      </c>
+      <c r="I951" t="n">
+        <v>3464.16</v>
+      </c>
+      <c r="J951" t="n">
+        <v>-30600</v>
+      </c>
+      <c r="K951" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B952" t="n">
+        <v>64759</v>
+      </c>
+      <c r="C952" t="n">
+        <v>64759</v>
+      </c>
+      <c r="D952" t="n">
+        <v>37407.17</v>
+      </c>
+      <c r="E952" t="n">
+        <v>27352</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0</v>
+      </c>
+      <c r="G952" t="n">
+        <v>0</v>
+      </c>
+      <c r="H952" t="n">
+        <v>0</v>
+      </c>
+      <c r="I952" t="n">
+        <v>2872.89</v>
+      </c>
+      <c r="J952" t="n">
+        <v>-27352</v>
+      </c>
+      <c r="K952" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B953" t="n">
+        <v>65910</v>
+      </c>
+      <c r="C953" t="n">
+        <v>65910</v>
+      </c>
+      <c r="D953" t="n">
+        <v>37403</v>
+      </c>
+      <c r="E953" t="n">
+        <v>28507</v>
+      </c>
+      <c r="F953" t="n">
+        <v>0</v>
+      </c>
+      <c r="G953" t="n">
+        <v>0</v>
+      </c>
+      <c r="H953" t="n">
+        <v>0</v>
+      </c>
+      <c r="I953" t="n">
+        <v>3005.54</v>
+      </c>
+      <c r="J953" t="n">
+        <v>-28507</v>
+      </c>
+      <c r="K953" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B954" t="n">
+        <v>70706</v>
+      </c>
+      <c r="C954" t="n">
+        <v>70706</v>
+      </c>
+      <c r="D954" t="n">
+        <v>37834</v>
+      </c>
+      <c r="E954" t="n">
+        <v>32854</v>
+      </c>
+      <c r="F954" t="n">
+        <v>0</v>
+      </c>
+      <c r="G954" t="n">
+        <v>0</v>
+      </c>
+      <c r="H954" t="n">
+        <v>0</v>
+      </c>
+      <c r="I954" t="n">
+        <v>2922.592</v>
+      </c>
+      <c r="J954" t="n">
+        <v>-32854</v>
+      </c>
+      <c r="K954" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B955" t="n">
+        <v>66692</v>
+      </c>
+      <c r="C955" t="n">
+        <v>66692</v>
+      </c>
+      <c r="D955" t="n">
+        <v>37057</v>
+      </c>
+      <c r="E955" t="n">
+        <v>29634</v>
+      </c>
+      <c r="F955" t="n">
+        <v>0</v>
+      </c>
+      <c r="G955" t="n">
+        <v>0</v>
+      </c>
+      <c r="H955" t="n">
+        <v>0</v>
+      </c>
+      <c r="I955" t="n">
+        <v>2684</v>
+      </c>
+      <c r="J955" t="n">
+        <v>-29634</v>
+      </c>
+      <c r="K955" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B956" t="n">
+        <v>61971</v>
+      </c>
+      <c r="C956" t="n">
+        <v>61971</v>
+      </c>
+      <c r="D956" t="n">
+        <v>36965</v>
+      </c>
+      <c r="F956" t="n">
+        <v>0</v>
+      </c>
+      <c r="G956" t="n">
+        <v>0</v>
+      </c>
+      <c r="H956" t="n">
+        <v>0</v>
+      </c>
+      <c r="I956" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J956" t="n">
+        <v>0</v>
+      </c>
+      <c r="K956" t="n">
+        <v>25006</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B957" t="n">
+        <v>58959</v>
+      </c>
+      <c r="C957" t="n">
+        <v>58959</v>
+      </c>
+      <c r="D957" t="n">
+        <v>36582</v>
+      </c>
+      <c r="E957" t="n">
+        <v>22376</v>
+      </c>
+      <c r="F957" t="n">
+        <v>0</v>
+      </c>
+      <c r="G957" t="n">
+        <v>0</v>
+      </c>
+      <c r="H957" t="n">
+        <v>0</v>
+      </c>
+      <c r="I957" t="n">
+        <v>2642.43</v>
+      </c>
+      <c r="J957" t="n">
+        <v>-22376</v>
+      </c>
+      <c r="K957" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B958" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C958" t="n">
+        <v>57306</v>
+      </c>
+      <c r="D958" t="n">
+        <v>33926.4</v>
+      </c>
+      <c r="E958" t="n">
+        <v>23379</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>0</v>
+      </c>
+      <c r="H958" t="n">
+        <v>0</v>
+      </c>
+      <c r="I958" t="n">
+        <v>2486.28</v>
+      </c>
+      <c r="J958" t="n">
+        <v>-23379</v>
+      </c>
+      <c r="K958" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B959" t="n">
+        <v>53992</v>
+      </c>
+      <c r="C959" t="n">
+        <v>53992</v>
+      </c>
+      <c r="D959" t="n">
+        <v>35897.751</v>
+      </c>
+      <c r="E959" t="n">
+        <v>15563</v>
+      </c>
+      <c r="F959" t="n">
+        <v>0</v>
+      </c>
+      <c r="G959" t="n">
+        <v>0</v>
+      </c>
+      <c r="H959" t="n">
+        <v>0</v>
+      </c>
+      <c r="I959" t="n">
+        <v>2530.718</v>
+      </c>
+      <c r="J959" t="n">
+        <v>-15563</v>
+      </c>
+      <c r="K959" t="n">
+        <v>2531.2</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B960" t="n">
+        <v>52159</v>
+      </c>
+      <c r="C960" t="n">
+        <v>52159</v>
+      </c>
+      <c r="D960" t="n">
+        <v>36295.604</v>
+      </c>
+      <c r="E960" t="n">
+        <v>13376</v>
+      </c>
+      <c r="F960" t="n">
+        <v>0</v>
+      </c>
+      <c r="G960" t="n">
+        <v>0</v>
+      </c>
+      <c r="H960" t="n">
+        <v>0</v>
+      </c>
+      <c r="I960" t="n">
+        <v>2487.93</v>
+      </c>
+      <c r="J960" t="n">
+        <v>-13376</v>
+      </c>
+      <c r="K960" t="n">
+        <v>2487.4</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B961" t="n">
+        <v>52598.06</v>
+      </c>
+      <c r="C961" t="n">
+        <v>52598.06</v>
+      </c>
+      <c r="D961" t="n">
+        <v>36495.19</v>
+      </c>
+      <c r="E961" t="n">
+        <v>16102.86</v>
+      </c>
+      <c r="F961" t="n">
+        <v>0</v>
+      </c>
+      <c r="G961" t="n">
+        <v>0</v>
+      </c>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" t="n">
+        <v>2231.85</v>
+      </c>
+      <c r="J961" t="n">
+        <v>-16102.86</v>
+      </c>
+      <c r="K961" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B962" t="n">
+        <v>50339</v>
+      </c>
+      <c r="C962" t="n">
+        <v>50339</v>
+      </c>
+      <c r="D962" t="n">
+        <v>36262.2</v>
+      </c>
+      <c r="E962" t="n">
+        <v>14077</v>
+      </c>
+      <c r="F962" t="n">
+        <v>0</v>
+      </c>
+      <c r="G962" t="n">
+        <v>0</v>
+      </c>
+      <c r="H962" t="n">
+        <v>0</v>
+      </c>
+      <c r="I962" t="n">
+        <v>2239.187</v>
+      </c>
+      <c r="J962" t="n">
+        <v>-14077</v>
+      </c>
+      <c r="K962" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B963" t="n">
+        <v>47778</v>
+      </c>
+      <c r="C963" t="n">
+        <v>47778</v>
+      </c>
+      <c r="D963" t="n">
+        <v>36251.111</v>
+      </c>
+      <c r="E963" t="n">
+        <v>11527</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0</v>
+      </c>
+      <c r="G963" t="n">
+        <v>0</v>
+      </c>
+      <c r="H963" t="n">
+        <v>0</v>
+      </c>
+      <c r="I963" t="n">
+        <v>2086.877</v>
+      </c>
+      <c r="J963" t="n">
+        <v>-11527</v>
+      </c>
+      <c r="K963" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B964" t="n">
+        <v>47651</v>
+      </c>
+      <c r="C964" t="n">
+        <v>47651</v>
+      </c>
+      <c r="D964" t="n">
+        <v>36277.003</v>
+      </c>
+      <c r="E964" t="n">
+        <v>11374</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0</v>
+      </c>
+      <c r="G964" t="n">
+        <v>0</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="n">
+        <v>1678.097</v>
+      </c>
+      <c r="J964" t="n">
+        <v>-11374</v>
+      </c>
+      <c r="K964" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B965" t="n">
+        <v>46015</v>
+      </c>
+      <c r="C965" t="n">
+        <v>46015</v>
+      </c>
+      <c r="D965" t="n">
+        <v>36266.052</v>
+      </c>
+      <c r="E965" t="n">
+        <v>9749</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0</v>
+      </c>
+      <c r="G965" t="n">
+        <v>0</v>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+      <c r="I965" t="n">
+        <v>1965.2</v>
+      </c>
+      <c r="J965" t="n">
+        <v>-9749</v>
+      </c>
+      <c r="K965" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B966" t="n">
+        <v>43297</v>
+      </c>
+      <c r="C966" t="n">
+        <v>43297</v>
+      </c>
+      <c r="D966" t="n">
+        <v>31925</v>
+      </c>
+      <c r="E966" t="n">
+        <v>11372</v>
+      </c>
+      <c r="F966" t="n">
+        <v>0</v>
+      </c>
+      <c r="G966" t="n">
+        <v>0</v>
+      </c>
+      <c r="H966" t="n">
+        <v>0</v>
+      </c>
+      <c r="I966" t="n">
+        <v>2112</v>
+      </c>
+      <c r="J966" t="n">
+        <v>-11372</v>
+      </c>
+      <c r="K966" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B967" t="n">
+        <v>43078</v>
+      </c>
+      <c r="C967" t="n">
+        <v>43078</v>
+      </c>
+      <c r="D967" t="n">
+        <v>32393</v>
+      </c>
+      <c r="E967" t="n">
+        <v>10656</v>
+      </c>
+      <c r="F967" t="n">
+        <v>0</v>
+      </c>
+      <c r="G967" t="n">
+        <v>0</v>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" t="n">
+        <v>1100.597</v>
+      </c>
+      <c r="J967" t="n">
+        <v>-10656</v>
+      </c>
+      <c r="K967" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B968" t="n">
+        <v>42012</v>
+      </c>
+      <c r="C968" t="n">
+        <v>42012</v>
+      </c>
+      <c r="D968" t="n">
+        <v>35384.278</v>
+      </c>
+      <c r="E968" t="n">
+        <v>6628</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0</v>
+      </c>
+      <c r="G968" t="n">
+        <v>0</v>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+      <c r="I968" t="n">
+        <v>515.585</v>
+      </c>
+      <c r="J968" t="n">
+        <v>-6628</v>
+      </c>
+      <c r="K968" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B969" t="n">
+        <v>40003</v>
+      </c>
+      <c r="C969" t="n">
+        <v>40003</v>
+      </c>
+      <c r="D969" t="n">
+        <v>35447.947</v>
+      </c>
+      <c r="E969" t="n">
+        <v>4555</v>
+      </c>
+      <c r="F969" t="n">
+        <v>0</v>
+      </c>
+      <c r="G969" t="n">
+        <v>0</v>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" t="n">
+        <v>0</v>
+      </c>
+      <c r="J969" t="n">
+        <v>-4555</v>
+      </c>
+      <c r="K969" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -34854,7 +35587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B948"/>
+  <dimension ref="A1:B969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42437,6 +43170,174 @@
       </c>
       <c r="B948" t="n">
         <v>1566.26</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B949" t="n">
+        <v>1609.36</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B950" t="n">
+        <v>1588.27</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B951" t="n">
+        <v>1623.67</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B952" t="n">
+        <v>1615.62</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B953" t="n">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B954" t="n">
+        <v>1632.59</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B955" t="n">
+        <v>1596.73</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B956" t="n">
+        <v>1603.59</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B957" t="n">
+        <v>1572.29</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B958" t="n">
+        <v>1645.81</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B959" t="n">
+        <v>1568.57</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B960" t="n">
+        <v>1575.22</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B961" t="n">
+        <v>1612.94</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B962" t="n">
+        <v>1543.43</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B963" t="n">
+        <v>1573.16</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B964" t="n">
+        <v>1562.89</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B965" t="n">
+        <v>1561.98</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B966" t="n">
+        <v>1561.04</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B967" t="n">
+        <v>1555.53</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B968" t="n">
+        <v>1526.8</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B969" t="n">
+        <v>1540.98</v>
       </c>
     </row>
   </sheetData>
@@ -42450,7 +43351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43369,6 +44270,22 @@
       </c>
       <c r="D57" t="n">
         <v>49326</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Exports_MWh</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2873</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23379</v>
       </c>
     </row>
   </sheetData>
@@ -43382,7 +44299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H948"/>
+  <dimension ref="A1:H969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67791,6 +68708,552 @@
         <v>0</v>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B949" t="n">
+        <v>76416</v>
+      </c>
+      <c r="C949" t="n">
+        <v>37240.951</v>
+      </c>
+      <c r="D949" t="n">
+        <v>1609.36</v>
+      </c>
+      <c r="E949" t="n">
+        <v>39176</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0</v>
+      </c>
+      <c r="G949" t="n">
+        <v>2682.375</v>
+      </c>
+      <c r="H949" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B950" t="n">
+        <v>75772</v>
+      </c>
+      <c r="C950" t="n">
+        <v>36687.69</v>
+      </c>
+      <c r="D950" t="n">
+        <v>1588.27</v>
+      </c>
+      <c r="E950" t="n">
+        <v>39085</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0</v>
+      </c>
+      <c r="G950" t="n">
+        <v>32836.5</v>
+      </c>
+      <c r="H950" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B951" t="n">
+        <v>67720</v>
+      </c>
+      <c r="C951" t="n">
+        <v>37120.13</v>
+      </c>
+      <c r="D951" t="n">
+        <v>1623.67</v>
+      </c>
+      <c r="E951" t="n">
+        <v>30600</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0</v>
+      </c>
+      <c r="G951" t="n">
+        <v>3464.16</v>
+      </c>
+      <c r="H951" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B952" t="n">
+        <v>64759</v>
+      </c>
+      <c r="C952" t="n">
+        <v>37407.17</v>
+      </c>
+      <c r="D952" t="n">
+        <v>1615.62</v>
+      </c>
+      <c r="E952" t="n">
+        <v>27352</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0</v>
+      </c>
+      <c r="G952" t="n">
+        <v>2872.89</v>
+      </c>
+      <c r="H952" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B953" t="n">
+        <v>65910</v>
+      </c>
+      <c r="C953" t="n">
+        <v>37403</v>
+      </c>
+      <c r="D953" t="n">
+        <v>1608</v>
+      </c>
+      <c r="E953" t="n">
+        <v>28507</v>
+      </c>
+      <c r="F953" t="n">
+        <v>0</v>
+      </c>
+      <c r="G953" t="n">
+        <v>3005.54</v>
+      </c>
+      <c r="H953" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B954" t="n">
+        <v>70706</v>
+      </c>
+      <c r="C954" t="n">
+        <v>37834</v>
+      </c>
+      <c r="D954" t="n">
+        <v>1632.59</v>
+      </c>
+      <c r="E954" t="n">
+        <v>32854</v>
+      </c>
+      <c r="F954" t="n">
+        <v>0</v>
+      </c>
+      <c r="G954" t="n">
+        <v>2922.592</v>
+      </c>
+      <c r="H954" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B955" t="n">
+        <v>66692</v>
+      </c>
+      <c r="C955" t="n">
+        <v>37057</v>
+      </c>
+      <c r="D955" t="n">
+        <v>1596.73</v>
+      </c>
+      <c r="E955" t="n">
+        <v>29634</v>
+      </c>
+      <c r="F955" t="n">
+        <v>0</v>
+      </c>
+      <c r="G955" t="n">
+        <v>2684</v>
+      </c>
+      <c r="H955" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B956" t="n">
+        <v>61971</v>
+      </c>
+      <c r="C956" t="n">
+        <v>36965</v>
+      </c>
+      <c r="D956" t="n">
+        <v>1603.59</v>
+      </c>
+      <c r="E956" t="n">
+        <v>2873</v>
+      </c>
+      <c r="F956" t="n">
+        <v>0</v>
+      </c>
+      <c r="G956" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H956" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B957" t="n">
+        <v>58959</v>
+      </c>
+      <c r="C957" t="n">
+        <v>36582</v>
+      </c>
+      <c r="D957" t="n">
+        <v>1572.29</v>
+      </c>
+      <c r="E957" t="n">
+        <v>22376</v>
+      </c>
+      <c r="F957" t="n">
+        <v>0</v>
+      </c>
+      <c r="G957" t="n">
+        <v>2642.43</v>
+      </c>
+      <c r="H957" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B958" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C958" t="n">
+        <v>33926.4</v>
+      </c>
+      <c r="D958" t="n">
+        <v>1645.81</v>
+      </c>
+      <c r="E958" t="n">
+        <v>23379</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>2486.28</v>
+      </c>
+      <c r="H958" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B959" t="n">
+        <v>53992</v>
+      </c>
+      <c r="C959" t="n">
+        <v>35897.751</v>
+      </c>
+      <c r="D959" t="n">
+        <v>1568.57</v>
+      </c>
+      <c r="E959" t="n">
+        <v>15563</v>
+      </c>
+      <c r="F959" t="n">
+        <v>0</v>
+      </c>
+      <c r="G959" t="n">
+        <v>2530.718</v>
+      </c>
+      <c r="H959" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B960" t="n">
+        <v>52159</v>
+      </c>
+      <c r="C960" t="n">
+        <v>36295.604</v>
+      </c>
+      <c r="D960" t="n">
+        <v>1575.22</v>
+      </c>
+      <c r="E960" t="n">
+        <v>13376</v>
+      </c>
+      <c r="F960" t="n">
+        <v>0</v>
+      </c>
+      <c r="G960" t="n">
+        <v>2487.93</v>
+      </c>
+      <c r="H960" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B961" t="n">
+        <v>52598.06</v>
+      </c>
+      <c r="C961" t="n">
+        <v>36495.19</v>
+      </c>
+      <c r="D961" t="n">
+        <v>1612.94</v>
+      </c>
+      <c r="E961" t="n">
+        <v>16102.86</v>
+      </c>
+      <c r="F961" t="n">
+        <v>0</v>
+      </c>
+      <c r="G961" t="n">
+        <v>2231.85</v>
+      </c>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B962" t="n">
+        <v>50339</v>
+      </c>
+      <c r="C962" t="n">
+        <v>36262.2</v>
+      </c>
+      <c r="D962" t="n">
+        <v>1543.43</v>
+      </c>
+      <c r="E962" t="n">
+        <v>14077</v>
+      </c>
+      <c r="F962" t="n">
+        <v>0</v>
+      </c>
+      <c r="G962" t="n">
+        <v>2239.187</v>
+      </c>
+      <c r="H962" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B963" t="n">
+        <v>47778</v>
+      </c>
+      <c r="C963" t="n">
+        <v>36251.111</v>
+      </c>
+      <c r="D963" t="n">
+        <v>1573.16</v>
+      </c>
+      <c r="E963" t="n">
+        <v>11527</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0</v>
+      </c>
+      <c r="G963" t="n">
+        <v>2086.877</v>
+      </c>
+      <c r="H963" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B964" t="n">
+        <v>47651</v>
+      </c>
+      <c r="C964" t="n">
+        <v>36277.003</v>
+      </c>
+      <c r="D964" t="n">
+        <v>1562.89</v>
+      </c>
+      <c r="E964" t="n">
+        <v>11374</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0</v>
+      </c>
+      <c r="G964" t="n">
+        <v>1678.097</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B965" t="n">
+        <v>46015</v>
+      </c>
+      <c r="C965" t="n">
+        <v>36266.052</v>
+      </c>
+      <c r="D965" t="n">
+        <v>1561.98</v>
+      </c>
+      <c r="E965" t="n">
+        <v>9749</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0</v>
+      </c>
+      <c r="G965" t="n">
+        <v>1965.2</v>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B966" t="n">
+        <v>43297</v>
+      </c>
+      <c r="C966" t="n">
+        <v>31925</v>
+      </c>
+      <c r="D966" t="n">
+        <v>1561.04</v>
+      </c>
+      <c r="E966" t="n">
+        <v>11372</v>
+      </c>
+      <c r="F966" t="n">
+        <v>0</v>
+      </c>
+      <c r="G966" t="n">
+        <v>2112</v>
+      </c>
+      <c r="H966" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B967" t="n">
+        <v>43078</v>
+      </c>
+      <c r="C967" t="n">
+        <v>32393</v>
+      </c>
+      <c r="D967" t="n">
+        <v>1555.53</v>
+      </c>
+      <c r="E967" t="n">
+        <v>10656</v>
+      </c>
+      <c r="F967" t="n">
+        <v>0</v>
+      </c>
+      <c r="G967" t="n">
+        <v>1100.597</v>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B968" t="n">
+        <v>42012</v>
+      </c>
+      <c r="C968" t="n">
+        <v>35384.278</v>
+      </c>
+      <c r="D968" t="n">
+        <v>1526.8</v>
+      </c>
+      <c r="E968" t="n">
+        <v>6628</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0</v>
+      </c>
+      <c r="G968" t="n">
+        <v>515.585</v>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B969" t="n">
+        <v>40003</v>
+      </c>
+      <c r="C969" t="n">
+        <v>35447.947</v>
+      </c>
+      <c r="D969" t="n">
+        <v>1540.98</v>
+      </c>
+      <c r="E969" t="n">
+        <v>4555</v>
+      </c>
+      <c r="F969" t="n">
+        <v>0</v>
+      </c>
+      <c r="G969" t="n">
+        <v>0</v>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
